--- a/diseases/d046/2026-2029.xlsx
+++ b/diseases/d046/2026-2029.xlsx
@@ -1729,6 +1729,154 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D046</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>filariasis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Filariasis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D046</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Filariasis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>丝虫病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1762,7 +1910,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1855,7 +2003,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d046/2026-2029.xlsx
+++ b/diseases/d046/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1314,6 +1319,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1852,6 +1862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2000,6 +2015,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2148,6 +2168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3076,6 +3101,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6344,6 +6374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10000,6 +10035,11 @@
       <c r="S51" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
